--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T09:27:52+00:00</t>
+    <t>2026-02-13T10:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,6 +499,167 @@
     <t>Need to be able to track the patient by multiple names. Examples are your official name and a partner name.</t>
   </si>
   <si>
+    <t>Patient.name.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Patient.name.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>Patient.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>Patient.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>Patient.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>Patient.name.prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>Patient.name.suffix</t>
+  </si>
+  <si>
+    <t>Parts that come after the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>Patient.name.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
     <t>Patient.telecom</t>
   </si>
   <si>
@@ -531,9 +692,6 @@
   </si>
   <si>
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>The gender of a person used for administrative purposes.</t>
@@ -691,26 +849,7 @@
     <t>Patient.contact.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Patient.contact.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -814,10 +953,6 @@
   </si>
   <si>
     <t>Patient.contact.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>The period during which this contact person or organization is valid to be contacted relating to this patient</t>
@@ -1276,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK46"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.92578125" customWidth="true" bestFit="true"/>
@@ -1308,7 +1443,7 @@
     <col min="27" max="27" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2712,7 +2847,7 @@
         <v>74</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>20</v>
@@ -2721,7 +2856,7 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>155</v>
@@ -2732,12 +2867,8 @@
       <c r="N14" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="P14" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
       <c r="Q14" t="s" s="2">
         <v>20</v>
       </c>
@@ -2785,19 +2916,19 @@
         <v>20</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -2805,21 +2936,21 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -2828,23 +2959,21 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="P15" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="P15" s="2"/>
       <c r="Q15" t="s" s="2">
         <v>20</v>
       </c>
@@ -2868,43 +2997,43 @@
         <v>20</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="AE15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
@@ -2912,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -2932,25 +3061,25 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P16" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="P16" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="Q16" t="s" s="2">
         <v>20</v>
@@ -2975,13 +3104,13 @@
         <v>20</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AB16" t="s" s="2">
         <v>20</v>
@@ -2999,7 +3128,7 @@
         <v>20</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>74</v>
@@ -3039,25 +3168,25 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="O17" t="s" s="2">
+      <c r="P17" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="P17" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="Q17" t="s" s="2">
         <v>20</v>
@@ -3106,7 +3235,7 @@
         <v>20</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>74</v>
@@ -3133,17 +3262,17 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>20</v>
@@ -3152,7 +3281,7 @@
         <v>82</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>182</v>
@@ -3163,9 +3292,7 @@
       <c r="O18" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="P18" t="s" s="2">
-        <v>185</v>
-      </c>
+      <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3213,13 +3340,13 @@
         <v>20</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>20</v>
@@ -3240,26 +3367,26 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="M19" t="s" s="2">
         <v>188</v>
@@ -3267,10 +3394,10 @@
       <c r="N19" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>190</v>
       </c>
+      <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3294,37 +3421,37 @@
         <v>20</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG19" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="AH19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>20</v>
@@ -3338,10 +3465,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -3352,7 +3479,7 @@
         <v>74</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
@@ -3361,23 +3488,19 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
         <v>20</v>
       </c>
@@ -3425,13 +3548,13 @@
         <v>20</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>20</v>
@@ -3445,10 +3568,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -3468,23 +3591,19 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
         <v>20</v>
       </c>
@@ -3532,7 +3651,7 @@
         <v>20</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>74</v>
@@ -3552,10 +3671,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -3566,7 +3685,7 @@
         <v>74</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -3575,22 +3694,20 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="Q22" t="s" s="2">
         <v>20</v>
@@ -3639,19 +3756,19 @@
         <v>20</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>212</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
@@ -3659,10 +3776,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -3673,7 +3790,7 @@
         <v>74</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -3682,19 +3799,23 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P23" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="Q23" t="s" s="2">
         <v>20</v>
       </c>
@@ -3742,19 +3863,19 @@
         <v>20</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
@@ -3762,21 +3883,21 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -3785,21 +3906,23 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P24" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="P24" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="Q24" t="s" s="2">
         <v>20</v>
       </c>
@@ -3823,13 +3946,13 @@
         <v>20</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="AB24" t="s" s="2">
         <v>20</v>
@@ -3847,19 +3970,19 @@
         <v>20</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
@@ -3867,45 +3990,45 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="M25" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="P25" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P25" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="Q25" t="s" s="2">
         <v>20</v>
@@ -3954,19 +4077,19 @@
         <v>20</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26">
@@ -3974,10 +4097,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -3988,19 +4111,19 @@
         <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>227</v>
@@ -4008,9 +4131,11 @@
       <c r="N26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q26" t="s" s="2">
         <v>20</v>
@@ -4035,13 +4160,13 @@
         <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
         <v>20</v>
@@ -4059,13 +4184,13 @@
         <v>20</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>20</v>
@@ -4079,10 +4204,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -4093,7 +4218,7 @@
         <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
@@ -4102,10 +4227,10 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>233</v>
@@ -4113,9 +4238,11 @@
       <c r="N27" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q27" t="s" s="2">
         <v>20</v>
@@ -4164,13 +4291,13 @@
         <v>20</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>20</v>
@@ -4184,10 +4311,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4198,7 +4325,7 @@
         <v>74</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
@@ -4210,19 +4337,17 @@
         <v>20</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>20</v>
@@ -4247,13 +4372,13 @@
         <v>20</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="AB28" t="s" s="2">
         <v>20</v>
@@ -4271,13 +4396,13 @@
         <v>20</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>20</v>
@@ -4291,10 +4416,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4317,17 +4442,19 @@
         <v>20</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P29" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="Q29" t="s" s="2">
         <v>20</v>
@@ -4376,7 +4503,7 @@
         <v>20</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>74</v>
@@ -4396,10 +4523,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4410,7 +4537,7 @@
         <v>74</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -4422,17 +4549,19 @@
         <v>20</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>101</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P30" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="Q30" t="s" s="2">
         <v>20</v>
@@ -4457,13 +4586,13 @@
         <v>20</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
         <v>20</v>
@@ -4481,13 +4610,13 @@
         <v>20</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>20</v>
@@ -4501,10 +4630,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -4515,7 +4644,7 @@
         <v>74</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -4527,17 +4656,19 @@
         <v>20</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P31" t="s" s="2">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="Q31" t="s" s="2">
         <v>20</v>
@@ -4586,19 +4717,19 @@
         <v>20</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>93</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32">
@@ -4606,10 +4737,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -4632,13 +4763,13 @@
         <v>20</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>254</v>
+        <v>155</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>255</v>
+        <v>156</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>256</v>
+        <v>157</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -4689,7 +4820,7 @@
         <v>20</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>253</v>
+        <v>158</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>74</v>
@@ -4701,7 +4832,7 @@
         <v>20</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -4709,14 +4840,14 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s" s="2">
@@ -4735,20 +4866,18 @@
         <v>20</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>207</v>
+        <v>125</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>258</v>
+        <v>126</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
         <v>20</v>
       </c>
@@ -4796,7 +4925,7 @@
         <v>20</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>257</v>
+        <v>164</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>74</v>
@@ -4808,7 +4937,7 @@
         <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34">
@@ -4816,42 +4945,46 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="Q34" t="s" s="2">
         <v>20</v>
       </c>
@@ -4899,19 +5032,19 @@
         <v>20</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>217</v>
+        <v>270</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35">
@@ -4919,14 +5052,14 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" t="s" s="2">
@@ -4945,18 +5078,18 @@
         <v>20</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>126</v>
+        <v>272</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="P35" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="Q35" t="s" s="2">
         <v>20</v>
       </c>
@@ -4980,13 +5113,13 @@
         <v>20</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="AB35" t="s" s="2">
         <v>20</v>
@@ -5004,7 +5137,7 @@
         <v>20</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>74</v>
@@ -5016,7 +5149,7 @@
         <v>20</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36">
@@ -5024,45 +5157,43 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c r="Q36" t="s" s="2">
         <v>20</v>
@@ -5111,19 +5242,19 @@
         <v>20</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
@@ -5131,10 +5262,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5142,10 +5273,10 @@
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -5157,19 +5288,19 @@
         <v>20</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>269</v>
+        <v>211</v>
       </c>
       <c r="Q37" t="s" s="2">
         <v>20</v>
@@ -5194,13 +5325,13 @@
         <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
         <v>20</v>
@@ -5218,13 +5349,13 @@
         <v>20</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>20</v>
@@ -5238,10 +5369,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5264,19 +5395,17 @@
         <v>20</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="Q38" t="s" s="2">
         <v>20</v>
@@ -5325,7 +5454,7 @@
         <v>20</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>74</v>
@@ -5345,21 +5474,21 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -5371,18 +5500,18 @@
         <v>20</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>101</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
+        <v>213</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="P39" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="Q39" t="s" s="2">
         <v>20</v>
       </c>
@@ -5406,13 +5535,13 @@
         <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="AB39" t="s" s="2">
         <v>20</v>
@@ -5430,13 +5559,13 @@
         <v>20</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>20</v>
@@ -5450,10 +5579,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5473,22 +5602,20 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="Q40" t="s" s="2">
         <v>20</v>
@@ -5537,7 +5664,7 @@
         <v>20</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>74</v>
@@ -5546,7 +5673,7 @@
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>93</v>
@@ -5557,10 +5684,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -5571,32 +5698,28 @@
         <v>74</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
         <v>20</v>
       </c>
@@ -5644,13 +5767,13 @@
         <v>20</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>20</v>
@@ -5664,10 +5787,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -5678,7 +5801,7 @@
         <v>74</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -5690,16 +5813,20 @@
         <v>20</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="Q42" t="s" s="2">
         <v>20</v>
       </c>
@@ -5747,19 +5874,19 @@
         <v>20</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>217</v>
+        <v>301</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43">
@@ -5767,21 +5894,21 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
@@ -5793,17 +5920,15 @@
         <v>20</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
         <v>20</v>
@@ -5852,19 +5977,19 @@
         <v>20</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -5872,14 +5997,14 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -5892,26 +6017,24 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>125</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="P44" t="s" s="2">
-        <v>134</v>
-      </c>
+      <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
         <v>20</v>
       </c>
@@ -5959,7 +6082,7 @@
         <v>20</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>225</v>
+        <v>164</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>74</v>
@@ -5979,44 +6102,46 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>295</v>
+        <v>125</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P45" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="Q45" t="s" s="2">
         <v>20</v>
       </c>
@@ -6064,19 +6189,19 @@
         <v>20</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46">
@@ -6084,10 +6209,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6107,19 +6232,23 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="Q46" t="s" s="2">
         <v>20</v>
       </c>
@@ -6143,13 +6272,13 @@
         <v>20</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>301</v>
+        <v>106</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="AB46" t="s" s="2">
         <v>20</v>
@@ -6167,7 +6296,7 @@
         <v>20</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>81</v>
@@ -6179,6 +6308,955 @@
         <v>20</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Q47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R47" s="2"/>
+      <c r="S47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="P48" s="2"/>
+      <c r="Q48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R48" s="2"/>
+      <c r="S48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Q49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R49" s="2"/>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Q50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R50" s="2"/>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R51" s="2"/>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R52" s="2"/>
+      <c r="S52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R53" s="2"/>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="P54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R54" s="2"/>
+      <c r="S54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="R55" s="2"/>
+      <c r="S55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK55" t="s" s="2">
         <v>93</v>
       </c>
     </row>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T10:55:57+00:00</t>
+    <t>2026-02-24T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T15:16:38+00:00</t>
+    <t>2026-02-24T15:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T15:20:34+00:00</t>
+    <t>2026-02-26T10:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
